--- a/전주공공와이파이.xlsx
+++ b/전주공공와이파이.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\양재우\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\example\publicWIFI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0986E9A5-D1B1-4775-ACB7-5CB26C77BC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A8C48B-5C04-48BD-9AD3-A50C0D72DDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-3765" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1185" uniqueCount="558">
   <si>
     <t>번호</t>
   </si>
@@ -88,1663 +88,1617 @@
     <t>Public WiFi Free</t>
   </si>
   <si>
+    <t>전북특별자치도 전주시 완산구 동완산동 464-1 전주시립도서관</t>
+  </si>
+  <si>
+    <t>전주시청</t>
+  </si>
+  <si>
+    <t>063-281-2300</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>평화도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화동2가 230-2 평화도서관</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>효자4동주민센터</t>
+  </si>
+  <si>
+    <t>민원실</t>
+  </si>
+  <si>
+    <t>관공서</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동 2가 1233-1</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구청</t>
+  </si>
+  <si>
+    <t>063-220-5500</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>효자3동주민센터</t>
+  </si>
+  <si>
+    <t>효자3동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 강변로 180</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동1가 296-36</t>
+  </si>
+  <si>
+    <t>35.8065593</t>
+  </si>
+  <si>
+    <t>127.1103409</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>효자2동주민센터</t>
+  </si>
+  <si>
+    <t>효자2동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 오두정1길 1</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동 1가 408-9</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>효자1동주민센터</t>
+  </si>
+  <si>
+    <t>hyoja1</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 안행5길 59-3</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동 1가 110-16</t>
+  </si>
+  <si>
+    <t>35.8058569</t>
+  </si>
+  <si>
+    <t>127.1300014</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>삼천3동주민센터</t>
+  </si>
+  <si>
+    <t>sam3</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 삼천천변2길 37</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 삼천동 1가 287-21</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>삼천2동주민센터</t>
+  </si>
+  <si>
+    <t>sam2</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 거마중앙로 49</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 삼천동 1가 633</t>
+  </si>
+  <si>
+    <t>35.7963168</t>
+  </si>
+  <si>
+    <t>127.1223579</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>삼천1동주민센터</t>
+  </si>
+  <si>
+    <t>sam1</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 성지산로 33</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 삼천동 1가 573-2</t>
+  </si>
+  <si>
+    <t>35.8008188</t>
+  </si>
+  <si>
+    <t>127.1216158</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>서신동주민센터</t>
+  </si>
+  <si>
+    <t>seoshin</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서신천변14길 10</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서신동 804-2</t>
+  </si>
+  <si>
+    <t>35.8309872</t>
+  </si>
+  <si>
+    <t>127.1153256</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>평화2동주민센터</t>
+  </si>
+  <si>
+    <t>평화2동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화18길 14-16</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화동 1가 720-4</t>
+  </si>
+  <si>
+    <t>35.7955181</t>
+  </si>
+  <si>
+    <t>127.135285</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>평화1동주민센터</t>
+  </si>
+  <si>
+    <t>평화1동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 장승배기로 256</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화동 1가 445-8</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>중화산2동주민센터</t>
+  </si>
+  <si>
+    <t>중화산2동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 화산천변로 30</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중화산동 2가 752-1</t>
+  </si>
+  <si>
+    <t>35.821654</t>
+  </si>
+  <si>
+    <t>127.1163942</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>중화산1동주민센터</t>
+  </si>
+  <si>
+    <t>iptime</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 한두평3길 16</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중화산동 2가 662</t>
+  </si>
+  <si>
+    <t>35.8145847</t>
+  </si>
+  <si>
+    <t>127.1248437</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>서서학동주민센터</t>
+  </si>
+  <si>
+    <t>서서학동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 공수내로24</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서서학동 23-8</t>
+  </si>
+  <si>
+    <t>35.8057276</t>
+  </si>
+  <si>
+    <t>127.1487117</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>동서학동주민센터</t>
+  </si>
+  <si>
+    <t>동서학동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서학로 26</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 동서학동 150</t>
+  </si>
+  <si>
+    <t>35.8094822</t>
+  </si>
+  <si>
+    <t>127.1522589</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>완산동주민센터</t>
+  </si>
+  <si>
+    <t>완산동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 강당2길 7</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서완산동 2가 71-31</t>
+  </si>
+  <si>
+    <t>35.8092187</t>
+  </si>
+  <si>
+    <t>127.1348687</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>노송동주민센터</t>
+  </si>
+  <si>
+    <t>노송동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 인봉1길 54</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중노송동 225</t>
+  </si>
+  <si>
+    <t>35.8243889</t>
+  </si>
+  <si>
+    <t>127.1583876</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>풍남동주민센터</t>
+  </si>
+  <si>
+    <t>풍남동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 어진길 122-12</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 경원동 1가 126-41</t>
+  </si>
+  <si>
+    <t>35.8170375</t>
+  </si>
+  <si>
+    <t>127.1481118</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>중앙동주민센터</t>
+  </si>
+  <si>
+    <t>중앙동</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평3길 43-17</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평동 32</t>
+  </si>
+  <si>
+    <t>35.8235043</t>
+  </si>
+  <si>
+    <t>127.1406401</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>완산구청</t>
+  </si>
+  <si>
+    <t>wansan</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서원로 232</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동 1가 595</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>덕진구청</t>
+  </si>
+  <si>
+    <t>SKT</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 벚꽃로 55</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 진북동 416-12</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구청</t>
+  </si>
+  <si>
+    <t>063-270-6200</t>
+  </si>
+  <si>
+    <t>35.829451</t>
+  </si>
+  <si>
+    <t>127.134205</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>1층(가족청소년과)</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>로비</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1층(자원위생과)</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>금평공원</t>
+  </si>
+  <si>
+    <t>편의시설</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 명주4길 9(인후동2가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동2가 1556-1</t>
+  </si>
+  <si>
+    <t>35.845138</t>
+  </si>
+  <si>
+    <t>127.149494</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>아중저수지입구</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인교9길 25(우아동1가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 우아동1가 1119-4</t>
+  </si>
+  <si>
+    <t>35.826149</t>
+  </si>
+  <si>
+    <t>127.175706</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>진북동주민센터</t>
+  </si>
+  <si>
+    <t>진북동센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 벚꽃1길 8</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 진북동 1042-4</t>
+  </si>
+  <si>
+    <t>35.827992</t>
+  </si>
+  <si>
+    <t>127.131469</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>인후1동주민센터</t>
+  </si>
+  <si>
+    <t>inhu</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 견훤로 290</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동 1가 766-9</t>
+  </si>
+  <si>
+    <t>35.8374601</t>
+  </si>
+  <si>
+    <t>127.156659</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>인후2동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 견훤왕궁로 244</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동 2가 26-8</t>
+  </si>
+  <si>
+    <t>35.8398462</t>
+  </si>
+  <si>
+    <t>127.1462397</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>인후3동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 구총목로 11</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동 1가 886-6</t>
+  </si>
+  <si>
+    <t>35.828363</t>
+  </si>
+  <si>
+    <t>127.1613387</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>덕진동주민센터</t>
+  </si>
+  <si>
+    <t>덕진동센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 기린대로 533-7</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 덕진동1가 1357-5</t>
+  </si>
+  <si>
+    <t>35.845585</t>
+  </si>
+  <si>
+    <t>127.120702</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>금암1동주민센터</t>
+  </si>
+  <si>
+    <t>olleh_wifi</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 기린대로 392</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 금암동 470-7</t>
+  </si>
+  <si>
+    <t>35.8374063</t>
+  </si>
+  <si>
+    <t>127.1331382</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>금암2동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 거북바우로 50</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 금암동 1572-1</t>
+  </si>
+  <si>
+    <t>35.8385429</t>
+  </si>
+  <si>
+    <t>127.143088</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>팔복동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 신복5길 6</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 팔복동 1가 138-6</t>
+  </si>
+  <si>
+    <t>35.8536276</t>
+  </si>
+  <si>
+    <t>127.1062727</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>우아1동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 우아2길 25</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 우아동 3가 746-67</t>
+  </si>
+  <si>
+    <t>35.8498168</t>
+  </si>
+  <si>
+    <t>127.1595847</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>우아2동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 진버들7길 25</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 우아동 2가 856-3</t>
+  </si>
+  <si>
+    <t>35.8377219</t>
+  </si>
+  <si>
+    <t>127.1670598</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>호성동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 동부대로 869</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 호성동 1가 863-44</t>
+  </si>
+  <si>
+    <t>35.8636502</t>
+  </si>
+  <si>
+    <t>127.149624</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>송천1동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천중앙로 116</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천동 1가 395-28</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>송천2동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 두간9길 6</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천동 1가 829-1</t>
+  </si>
+  <si>
+    <t>35.8648946</t>
+  </si>
+  <si>
+    <t>127.1156222</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>조촌동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 쪽구름로 150</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 반월동 394</t>
+  </si>
+  <si>
+    <t>35.8745192</t>
+  </si>
+  <si>
+    <t>127.0691918</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>여의동주민센터</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 여암2길 9</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 여의동 606-4</t>
+  </si>
+  <si>
+    <t>35.8710292</t>
+  </si>
+  <si>
+    <t>127.074519</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>혁신동주민센터</t>
+  </si>
+  <si>
+    <t>LG유플러스</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 오공로 43-24</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 중동 775-5</t>
+  </si>
+  <si>
+    <t>35.833958</t>
+  </si>
+  <si>
+    <t>127.062</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>전주향교</t>
+  </si>
+  <si>
+    <t>서제, 동제</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 향교길 139</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 교동 26-3</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시청</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>한옥마을 관광안내소</t>
+  </si>
+  <si>
+    <t>건물 밖</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 기린대로 99</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 남노송동 100-1</t>
+  </si>
+  <si>
+    <t>35.818223</t>
+  </si>
+  <si>
+    <t>127.153715</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>전주한옥생활체험관</t>
+  </si>
+  <si>
+    <t>중앙 건물</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 어진길 29</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 풍남동3가 33-4</t>
+  </si>
+  <si>
+    <t>35.8175156</t>
+  </si>
+  <si>
+    <t>127.1530223</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>전주농수산물도매시장</t>
+  </si>
+  <si>
+    <t>청과동 경매장 내</t>
+  </si>
+  <si>
+    <t>서민·복지시설</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 동부대로 1183</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천동2가 506-1</t>
+  </si>
+  <si>
+    <t>35.8673242</t>
+  </si>
+  <si>
+    <t>127.1178159</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>서부시장</t>
+  </si>
+  <si>
+    <t>포도원교회 옥상, 참다인 옥상</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효동2길 23</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동1가 205-12</t>
+  </si>
+  <si>
+    <t>35.8044308</t>
+  </si>
+  <si>
+    <t>127.1268368</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>중앙상가시장</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평3길 70</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평동 36-1</t>
+  </si>
+  <si>
+    <t>35.8252359</t>
+  </si>
+  <si>
+    <t>127.1424673</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>오목대 관광안내소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태조로6</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 풍남동3가 15-11</t>
+  </si>
+  <si>
+    <t>35.8151957</t>
+  </si>
+  <si>
+    <t>127.1539379</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>전주솔내청소년수련관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 동부대로 1079</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천동2가 170</t>
+  </si>
+  <si>
+    <t>35.8692026</t>
+  </si>
+  <si>
+    <t>127.1289651</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>전주정보문화사업진흥원</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 아중로 33</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중노송동 470-4</t>
+  </si>
+  <si>
+    <t>35.8238191</t>
+  </si>
+  <si>
+    <t>127.1537316</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>전주시외버스공영터미널</t>
+  </si>
+  <si>
+    <t>대합실 내</t>
+  </si>
+  <si>
+    <t>교통시설</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 가리내로 30</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 금암동 796-5</t>
+  </si>
+  <si>
+    <t>35.8347125</t>
+  </si>
+  <si>
+    <t>127.1324629</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>쪽구름도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 반월동 248-32</t>
+  </si>
+  <si>
+    <t>35.871346</t>
+  </si>
+  <si>
+    <t>127.0755889</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>건지도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 호성로 25</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 호성동1가 728</t>
+  </si>
+  <si>
+    <t>35.8542016</t>
+  </si>
+  <si>
+    <t>127.1515214</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>아중도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 무삼지2길 7</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동1가 907-1</t>
+  </si>
+  <si>
+    <t>35.826335</t>
+  </si>
+  <si>
+    <t>127.1626206</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>삼천도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 용리로 107</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 삼천동1가 182-1</t>
+  </si>
+  <si>
+    <t>35.7990541</t>
+  </si>
+  <si>
+    <t>127.121737</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>오거리광장</t>
+  </si>
+  <si>
+    <t>오거리 광장</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 팔달로 217-21</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 고사동 11-8</t>
+  </si>
+  <si>
+    <t>35.821371</t>
+  </si>
+  <si>
+    <t>127.1451392</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>경기전</t>
+  </si>
+  <si>
+    <t>사무실 내</t>
+  </si>
+  <si>
+    <t>관광</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태조로 44</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 풍남동3가 91-5</t>
+  </si>
+  <si>
+    <t>35.8143104</t>
+  </si>
+  <si>
+    <t>127.1501213</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>로비, 민원실, 쉼터, 시청광장</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 노송광장로 10</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서노송동 568-1</t>
+  </si>
+  <si>
+    <t>35.8244359</t>
+  </si>
+  <si>
+    <t>127.147807</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>한옥마을</t>
+  </si>
+  <si>
+    <t>중앙초등학교 사거리</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 경기전길 120</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 교동 269-3</t>
+  </si>
+  <si>
+    <t>35.814128</t>
+  </si>
+  <si>
+    <t>127.1510233</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>평화보건지소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화13길 7</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 평화동2가 862-6</t>
+  </si>
+  <si>
+    <t>35.790728</t>
+  </si>
+  <si>
+    <t>127.1366931</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>덕진보건소</t>
+  </si>
+  <si>
+    <t>35.8293589</t>
+  </si>
+  <si>
+    <t>127.1345616</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>전주보건소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전라감영로 33</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중앙동4가 30-1</t>
+  </si>
+  <si>
+    <t>35.8156251</t>
+  </si>
+  <si>
+    <t>127.1431738</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>차량등록사업소</t>
+  </si>
+  <si>
+    <t>민원실 내, 번호판 부착장소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 완주로 6</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 호성동2가 631-12</t>
+  </si>
+  <si>
+    <t>35.867429</t>
+  </si>
+  <si>
+    <t>127.1475595</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>모래내시장</t>
+  </si>
+  <si>
+    <t>시장 내</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 모래내5길 13-2</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동2가 203-1</t>
+  </si>
+  <si>
+    <t>35.8337911</t>
+  </si>
+  <si>
+    <t>127.1441961</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>전주신중앙시장</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평5길 33</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 태평동 41-5</t>
+  </si>
+  <si>
+    <t>35.8241424</t>
+  </si>
+  <si>
+    <t>127.1435316</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>남부시장</t>
+  </si>
+  <si>
+    <t>시장 내, 청년몰 전시장 등</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 풍남문2길 63</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전동3가 2-242</t>
+  </si>
+  <si>
+    <t>35.8124076</t>
+  </si>
+  <si>
+    <t>127.1465988</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>동물원</t>
+  </si>
+  <si>
+    <t>매표소 앞, 동물원 내 편의점 밖</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 소리로 68</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 덕진동1가 73-48</t>
+  </si>
+  <si>
+    <t>35.8561153</t>
+  </si>
+  <si>
+    <t>127.1446737</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>영화제작소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전주객사3길 22</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 고사동 429-5</t>
+  </si>
+  <si>
+    <t>35.8183489</t>
+  </si>
+  <si>
+    <t>127.1425492</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>전주전통문화연수원</t>
+  </si>
+  <si>
+    <t>동헌 건물</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 향교길 119-6</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 교동 28-2</t>
+  </si>
+  <si>
+    <t>35.8124679</t>
+  </si>
+  <si>
+    <t>127.1565548</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>전주한벽문화관</t>
+  </si>
+  <si>
+    <t>한벽극장 로비</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전주천동로 20</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 교동 7-1</t>
+  </si>
+  <si>
+    <t>35.8119867</t>
+  </si>
+  <si>
+    <t>127.158493</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>강암서예관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전주천동로 74</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 교동 197</t>
+  </si>
+  <si>
+    <t>35.811245</t>
+  </si>
+  <si>
+    <t>127.1524913</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>금암도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 거북바우로 13, 금암도서관 (금암동)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 금암동 1569-1 금암도서관</t>
+  </si>
+  <si>
+    <t>35.83653</t>
+  </si>
+  <si>
+    <t>127.114010</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>송천도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 솔내로 212, 송천도서관 (송천동2가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 송천동2가 168-5 송천도서관</t>
+  </si>
+  <si>
+    <t>35.86971</t>
+  </si>
+  <si>
+    <t>127.12805</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>인후도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 안덕원로 349, 전주시립인후도서관 (인후동1가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동1가 532-3 전주시립인후도서관</t>
+  </si>
+  <si>
+    <t>35.83972</t>
+  </si>
+  <si>
+    <t>127.16330</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>서신도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서신천변14길 10, 서신복합문화센터(도서관,서신주민센터) (서신동)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서신동 804 서신복합문화센터(도서관,서신주민센터)</t>
+  </si>
+  <si>
+    <t>35.83116</t>
+  </si>
+  <si>
+    <t>127.11505</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>효자도서관</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 우전로 181, 효자도서관 (효자동2가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동2가 1314-9 효자도서관</t>
+  </si>
+  <si>
+    <t>38.81112</t>
+  </si>
+  <si>
+    <t>127.10075</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>전주시립도서관 꽃심</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 백제대로 306(중화산동2가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 중화산동2가 산 66</t>
+  </si>
+  <si>
+    <t>35.82048</t>
+  </si>
+  <si>
+    <t>127.12359</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>완산구청 3층 정보화교육장</t>
+  </si>
+  <si>
+    <t>edu</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서원로 232, 완산구청 (효자동1가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동1가 595 완산구청</t>
+  </si>
+  <si>
+    <t>063-220-5300</t>
+  </si>
+  <si>
+    <t>35.81239</t>
+  </si>
+  <si>
+    <t>127.11982</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>효자5동주민센터</t>
+  </si>
+  <si>
+    <t>hyoja5</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 우전로 259, 효자5동주민센터 (효자동2가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 효자동2가 1233-1 효자5동주민센터</t>
+  </si>
+  <si>
+    <t>35.81784</t>
+  </si>
+  <si>
+    <t>127.10152</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>서학동예술마을</t>
+  </si>
+  <si>
+    <t>동서학동주민센터 옥상 외 3개소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서학3길 45, 일원 (서서학동)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 서서학동 3-6 서서학파출소</t>
+  </si>
+  <si>
+    <t>35.80884</t>
+  </si>
+  <si>
+    <t>127.15190</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>객리단길</t>
+  </si>
+  <si>
+    <t>어부바식당앞 외 3개소</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전주객사1길 12-7, 일원 (다가동3가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 다가동3가 24-1</t>
+  </si>
+  <si>
+    <t>35.81715</t>
+  </si>
+  <si>
+    <t>127.14027</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>아동청소년센터(야호학교)</t>
+  </si>
+  <si>
+    <t>교육시설</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 진버들5길 15-1(인후동1가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 덕진구 인후동1가 807-4</t>
+  </si>
+  <si>
+    <t>35.83649</t>
+  </si>
+  <si>
+    <t>127.16437</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>풍남문광장</t>
+  </si>
+  <si>
+    <t>광장</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 풍남문2길 105-6(전동3가)</t>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시 완산구 전동3가 77</t>
+  </si>
+  <si>
+    <t>35.81401</t>
+  </si>
+  <si>
+    <t>127.14809</t>
+  </si>
+  <si>
+    <t>Public WiFi Free</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hyoja4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>전북특별자치도 전주시 완산구 곤지산4길 12, 전주시립도서관 (동완산동)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 동완산동 464-1 전주시립도서관</t>
-  </si>
-  <si>
-    <t>전주시청</t>
-  </si>
-  <si>
-    <t>063-281-2300</t>
-  </si>
-  <si>
-    <t>35.80883</t>
-  </si>
-  <si>
-    <t>127.14799</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>평화도서관</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>전북특별자치도 전주시 완산구 평화14길 27-51, 평화도서관 (평화동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화동2가 230-2 평화도서관</t>
-  </si>
-  <si>
-    <t>35.79145</t>
-  </si>
-  <si>
-    <t>127.13488</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>효자4동주민센터</t>
-  </si>
-  <si>
-    <t>민원실</t>
-  </si>
-  <si>
-    <t>관공서</t>
-  </si>
-  <si>
-    <t>hyoja4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>전북특별자치도 전주시 완산구 우전로 259</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동 2가 1233-1</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구청</t>
-  </si>
-  <si>
-    <t>063-220-5500</t>
-  </si>
-  <si>
-    <t>35.8176718</t>
-  </si>
-  <si>
-    <t>127.1015345</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>효자3동주민센터</t>
-  </si>
-  <si>
-    <t>효자3동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 강변로 180</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동1가 296-36</t>
-  </si>
-  <si>
-    <t>35.8065593</t>
-  </si>
-  <si>
-    <t>127.1103409</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>효자2동주민센터</t>
-  </si>
-  <si>
-    <t>효자2동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 오두정1길 1</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동 1가 408-9</t>
-  </si>
-  <si>
-    <t>35.8068378</t>
-  </si>
-  <si>
-    <t>127.1195137</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>효자1동주민센터</t>
-  </si>
-  <si>
-    <t>hyoja1</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 안행5길 59-3</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동 1가 110-16</t>
-  </si>
-  <si>
-    <t>35.8058569</t>
-  </si>
-  <si>
-    <t>127.1300014</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>삼천3동주민센터</t>
-  </si>
-  <si>
-    <t>sam3</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 삼천천변2길 37</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 삼천동 1가 287-21</t>
-  </si>
-  <si>
-    <t>35.7968626</t>
-  </si>
-  <si>
-    <t>127.1143079</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>삼천2동주민센터</t>
-  </si>
-  <si>
-    <t>sam2</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 거마중앙로 49</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 삼천동 1가 633</t>
-  </si>
-  <si>
-    <t>35.7963168</t>
-  </si>
-  <si>
-    <t>127.1223579</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>삼천1동주민센터</t>
-  </si>
-  <si>
-    <t>sam1</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 성지산로 33</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 삼천동 1가 573-2</t>
-  </si>
-  <si>
-    <t>35.8008188</t>
-  </si>
-  <si>
-    <t>127.1216158</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>서신동주민센터</t>
-  </si>
-  <si>
-    <t>seoshin</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서신천변14길 10</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서신동 804-2</t>
-  </si>
-  <si>
-    <t>35.8309872</t>
-  </si>
-  <si>
-    <t>127.1153256</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>평화2동주민센터</t>
-  </si>
-  <si>
-    <t>평화2동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화18길 14-16</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화동 1가 720-4</t>
-  </si>
-  <si>
-    <t>35.7955181</t>
-  </si>
-  <si>
-    <t>127.135285</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>평화1동주민센터</t>
-  </si>
-  <si>
-    <t>평화1동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 장승배기로 256</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화동 1가 445-8</t>
-  </si>
-  <si>
-    <t>35.7980662</t>
-  </si>
-  <si>
-    <t>127.1403211</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>중화산2동주민센터</t>
-  </si>
-  <si>
-    <t>중화산2동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 화산천변로 30</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중화산동 2가 752-1</t>
-  </si>
-  <si>
-    <t>35.821654</t>
-  </si>
-  <si>
-    <t>127.1163942</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>중화산1동주민센터</t>
-  </si>
-  <si>
-    <t>iptime</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 한두평3길 16</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중화산동 2가 662</t>
-  </si>
-  <si>
-    <t>35.8145847</t>
-  </si>
-  <si>
-    <t>127.1248437</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>서서학동주민센터</t>
-  </si>
-  <si>
-    <t>서서학동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 공수내로24</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서서학동 23-8</t>
-  </si>
-  <si>
-    <t>35.8057276</t>
-  </si>
-  <si>
-    <t>127.1487117</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>동서학동주민센터</t>
-  </si>
-  <si>
-    <t>동서학동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서학로 26</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 동서학동 150</t>
-  </si>
-  <si>
-    <t>35.8094822</t>
-  </si>
-  <si>
-    <t>127.1522589</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>완산동주민센터</t>
-  </si>
-  <si>
-    <t>완산동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 강당2길 7</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서완산동 2가 71-31</t>
-  </si>
-  <si>
-    <t>35.8092187</t>
-  </si>
-  <si>
-    <t>127.1348687</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>노송동주민센터</t>
-  </si>
-  <si>
-    <t>노송동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 인봉1길 54</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중노송동 225</t>
-  </si>
-  <si>
-    <t>35.8243889</t>
-  </si>
-  <si>
-    <t>127.1583876</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>풍남동주민센터</t>
-  </si>
-  <si>
-    <t>풍남동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 어진길 122-12</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 경원동 1가 126-41</t>
-  </si>
-  <si>
-    <t>35.8170375</t>
-  </si>
-  <si>
-    <t>127.1481118</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>중앙동주민센터</t>
-  </si>
-  <si>
-    <t>중앙동</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평3길 43-17</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평동 32</t>
-  </si>
-  <si>
-    <t>35.8235043</t>
-  </si>
-  <si>
-    <t>127.1406401</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>완산구청</t>
-  </si>
-  <si>
-    <t>wansan</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서원로 232</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동 1가 595</t>
-  </si>
-  <si>
-    <t>35.812153</t>
-  </si>
-  <si>
-    <t>127.1198025</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>덕진구청</t>
-  </si>
-  <si>
-    <t>SKT</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 벚꽃로 55</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 진북동 416-12</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구청</t>
-  </si>
-  <si>
-    <t>063-270-6200</t>
-  </si>
-  <si>
-    <t>35.829451</t>
-  </si>
-  <si>
-    <t>127.134205</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>1층(가족청소년과)</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>로비</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>1층(자원위생과)</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>금평공원</t>
-  </si>
-  <si>
-    <t>편의시설</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 명주4길 9(인후동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동2가 1556-1</t>
-  </si>
-  <si>
-    <t>35.845138</t>
-  </si>
-  <si>
-    <t>127.149494</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>아중저수지입구</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인교9길 25(우아동1가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 우아동1가 1119-4</t>
-  </si>
-  <si>
-    <t>35.826149</t>
-  </si>
-  <si>
-    <t>127.175706</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>진북동주민센터</t>
-  </si>
-  <si>
-    <t>진북동센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 벚꽃1길 8</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 진북동 1042-4</t>
-  </si>
-  <si>
-    <t>35.827992</t>
-  </si>
-  <si>
-    <t>127.131469</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>인후1동주민센터</t>
-  </si>
-  <si>
-    <t>inhu</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 견훤로 290</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동 1가 766-9</t>
-  </si>
-  <si>
-    <t>35.8374601</t>
-  </si>
-  <si>
-    <t>127.156659</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>인후2동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 견훤왕궁로 244</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동 2가 26-8</t>
-  </si>
-  <si>
-    <t>35.8398462</t>
-  </si>
-  <si>
-    <t>127.1462397</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>인후3동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 구총목로 11</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동 1가 886-6</t>
-  </si>
-  <si>
-    <t>35.828363</t>
-  </si>
-  <si>
-    <t>127.1613387</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>덕진동주민센터</t>
-  </si>
-  <si>
-    <t>덕진동센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 기린대로 533-7</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 덕진동1가 1357-5</t>
-  </si>
-  <si>
-    <t>35.845585</t>
-  </si>
-  <si>
-    <t>127.120702</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>금암1동주민센터</t>
-  </si>
-  <si>
-    <t>olleh_wifi</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 기린대로 392</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 금암동 470-7</t>
-  </si>
-  <si>
-    <t>35.8374063</t>
-  </si>
-  <si>
-    <t>127.1331382</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>금암2동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 거북바우로 50</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 금암동 1572-1</t>
-  </si>
-  <si>
-    <t>35.8385429</t>
-  </si>
-  <si>
-    <t>127.143088</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>팔복동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 신복5길 6</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 팔복동 1가 138-6</t>
-  </si>
-  <si>
-    <t>35.8536276</t>
-  </si>
-  <si>
-    <t>127.1062727</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>우아1동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 우아2길 25</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 우아동 3가 746-67</t>
-  </si>
-  <si>
-    <t>35.8498168</t>
-  </si>
-  <si>
-    <t>127.1595847</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>우아2동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 진버들7길 25</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 우아동 2가 856-3</t>
-  </si>
-  <si>
-    <t>35.8377219</t>
-  </si>
-  <si>
-    <t>127.1670598</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>호성동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 동부대로 869</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 호성동 1가 863-44</t>
-  </si>
-  <si>
-    <t>35.8636502</t>
-  </si>
-  <si>
-    <t>127.149624</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>송천1동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천중앙로 116</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천동 1가 395-28</t>
-  </si>
-  <si>
-    <t>35.8570947</t>
-  </si>
-  <si>
-    <t>127.1210231</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>송천2동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 두간9길 6</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천동 1가 829-1</t>
-  </si>
-  <si>
-    <t>35.8648946</t>
-  </si>
-  <si>
-    <t>127.1156222</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>조촌동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 쪽구름로 150</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 반월동 394</t>
-  </si>
-  <si>
-    <t>35.8745192</t>
-  </si>
-  <si>
-    <t>127.0691918</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>여의동주민센터</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 여암2길 9</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 여의동 606-4</t>
-  </si>
-  <si>
-    <t>35.8710292</t>
-  </si>
-  <si>
-    <t>127.074519</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>혁신동주민센터</t>
-  </si>
-  <si>
-    <t>LG유플러스</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 오공로 43-24</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 중동 775-5</t>
-  </si>
-  <si>
-    <t>35.833958</t>
-  </si>
-  <si>
-    <t>127.062</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>전주향교</t>
-  </si>
-  <si>
-    <t>서제, 동제</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 향교길 139</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 교동 26-3</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시청</t>
-  </si>
-  <si>
-    <t>35.8128298</t>
-  </si>
-  <si>
-    <t>127.1571308</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>한옥마을 관광안내소</t>
-  </si>
-  <si>
-    <t>건물 밖</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 기린대로 99</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 남노송동 100-1</t>
-  </si>
-  <si>
-    <t>35.818223</t>
-  </si>
-  <si>
-    <t>127.153715</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>전주한옥생활체험관</t>
-  </si>
-  <si>
-    <t>중앙 건물</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 어진길 29</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 풍남동3가 33-4</t>
-  </si>
-  <si>
-    <t>35.8175156</t>
-  </si>
-  <si>
-    <t>127.1530223</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>전주농수산물도매시장</t>
-  </si>
-  <si>
-    <t>청과동 경매장 내</t>
-  </si>
-  <si>
-    <t>서민·복지시설</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 동부대로 1183</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천동2가 506-1</t>
-  </si>
-  <si>
-    <t>35.8673242</t>
-  </si>
-  <si>
-    <t>127.1178159</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>서부시장</t>
-  </si>
-  <si>
-    <t>포도원교회 옥상, 참다인 옥상</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효동2길 23</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동1가 205-12</t>
-  </si>
-  <si>
-    <t>35.8044308</t>
-  </si>
-  <si>
-    <t>127.1268368</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>중앙상가시장</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평3길 70</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평동 36-1</t>
-  </si>
-  <si>
-    <t>35.8252359</t>
-  </si>
-  <si>
-    <t>127.1424673</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>오목대 관광안내소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태조로6</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 풍남동3가 15-11</t>
-  </si>
-  <si>
-    <t>35.8151957</t>
-  </si>
-  <si>
-    <t>127.1539379</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>전주솔내청소년수련관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 동부대로 1079</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천동2가 170</t>
-  </si>
-  <si>
-    <t>35.8692026</t>
-  </si>
-  <si>
-    <t>127.1289651</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>전주정보문화사업진흥원</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 아중로 33</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중노송동 470-4</t>
-  </si>
-  <si>
-    <t>35.8238191</t>
-  </si>
-  <si>
-    <t>127.1537316</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>전주시외버스공영터미널</t>
-  </si>
-  <si>
-    <t>대합실 내</t>
-  </si>
-  <si>
-    <t>교통시설</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 가리내로 30</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 금암동 796-5</t>
-  </si>
-  <si>
-    <t>35.8347125</t>
-  </si>
-  <si>
-    <t>127.1324629</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>쪽구름도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 반월동 248-32</t>
-  </si>
-  <si>
-    <t>35.871346</t>
-  </si>
-  <si>
-    <t>127.0755889</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>건지도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 호성로 25</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 호성동1가 728</t>
-  </si>
-  <si>
-    <t>35.8542016</t>
-  </si>
-  <si>
-    <t>127.1515214</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>아중도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 무삼지2길 7</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동1가 907-1</t>
-  </si>
-  <si>
-    <t>35.826335</t>
-  </si>
-  <si>
-    <t>127.1626206</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>삼천도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 용리로 107</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 삼천동1가 182-1</t>
-  </si>
-  <si>
-    <t>35.7990541</t>
-  </si>
-  <si>
-    <t>127.121737</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>오거리광장</t>
-  </si>
-  <si>
-    <t>오거리 광장</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 팔달로 217-21</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 고사동 11-8</t>
-  </si>
-  <si>
-    <t>35.821371</t>
-  </si>
-  <si>
-    <t>127.1451392</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>경기전</t>
-  </si>
-  <si>
-    <t>사무실 내</t>
-  </si>
-  <si>
-    <t>관광</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태조로 44</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 풍남동3가 91-5</t>
-  </si>
-  <si>
-    <t>35.8143104</t>
-  </si>
-  <si>
-    <t>127.1501213</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>로비, 민원실, 쉼터, 시청광장</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 노송광장로 10</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서노송동 568-1</t>
-  </si>
-  <si>
-    <t>35.8244359</t>
-  </si>
-  <si>
-    <t>127.147807</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>한옥마을</t>
-  </si>
-  <si>
-    <t>중앙초등학교 사거리</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 경기전길 120</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 교동 269-3</t>
-  </si>
-  <si>
-    <t>35.814128</t>
-  </si>
-  <si>
-    <t>127.1510233</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>평화보건지소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화13길 7</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 평화동2가 862-6</t>
-  </si>
-  <si>
-    <t>35.790728</t>
-  </si>
-  <si>
-    <t>127.1366931</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>덕진보건소</t>
-  </si>
-  <si>
-    <t>35.8293589</t>
-  </si>
-  <si>
-    <t>127.1345616</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>전주보건소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전라감영로 33</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중앙동4가 30-1</t>
-  </si>
-  <si>
-    <t>35.8156251</t>
-  </si>
-  <si>
-    <t>127.1431738</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>차량등록사업소</t>
-  </si>
-  <si>
-    <t>민원실 내, 번호판 부착장소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 완주로 6</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 호성동2가 631-12</t>
-  </si>
-  <si>
-    <t>35.867429</t>
-  </si>
-  <si>
-    <t>127.1475595</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>모래내시장</t>
-  </si>
-  <si>
-    <t>시장 내</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 모래내5길 13-2</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동2가 203-1</t>
-  </si>
-  <si>
-    <t>35.8337911</t>
-  </si>
-  <si>
-    <t>127.1441961</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>전주신중앙시장</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평5길 33</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 태평동 41-5</t>
-  </si>
-  <si>
-    <t>35.8241424</t>
-  </si>
-  <si>
-    <t>127.1435316</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>남부시장</t>
-  </si>
-  <si>
-    <t>시장 내, 청년몰 전시장 등</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 풍남문2길 63</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전동3가 2-242</t>
-  </si>
-  <si>
-    <t>35.8124076</t>
-  </si>
-  <si>
-    <t>127.1465988</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t>동물원</t>
-  </si>
-  <si>
-    <t>매표소 앞, 동물원 내 편의점 밖</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 소리로 68</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 덕진동1가 73-48</t>
-  </si>
-  <si>
-    <t>35.8561153</t>
-  </si>
-  <si>
-    <t>127.1446737</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>영화제작소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전주객사3길 22</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 고사동 429-5</t>
-  </si>
-  <si>
-    <t>35.8183489</t>
-  </si>
-  <si>
-    <t>127.1425492</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>전주전통문화연수원</t>
-  </si>
-  <si>
-    <t>동헌 건물</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 향교길 119-6</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 교동 28-2</t>
-  </si>
-  <si>
-    <t>35.8124679</t>
-  </si>
-  <si>
-    <t>127.1565548</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>전주한벽문화관</t>
-  </si>
-  <si>
-    <t>한벽극장 로비</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전주천동로 20</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 교동 7-1</t>
-  </si>
-  <si>
-    <t>35.8119867</t>
-  </si>
-  <si>
-    <t>127.158493</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>강암서예관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전주천동로 74</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 교동 197</t>
-  </si>
-  <si>
-    <t>35.811245</t>
-  </si>
-  <si>
-    <t>127.1524913</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>금암도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 거북바우로 13, 금암도서관 (금암동)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 금암동 1569-1 금암도서관</t>
-  </si>
-  <si>
-    <t>35.83653</t>
-  </si>
-  <si>
-    <t>127.114010</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>송천도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 솔내로 212, 송천도서관 (송천동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 송천동2가 168-5 송천도서관</t>
-  </si>
-  <si>
-    <t>35.86971</t>
-  </si>
-  <si>
-    <t>127.12805</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>인후도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 안덕원로 349, 전주시립인후도서관 (인후동1가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동1가 532-3 전주시립인후도서관</t>
-  </si>
-  <si>
-    <t>35.83972</t>
-  </si>
-  <si>
-    <t>127.16330</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>서신도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서신천변14길 10, 서신복합문화센터(도서관,서신주민센터) (서신동)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서신동 804 서신복합문화센터(도서관,서신주민센터)</t>
-  </si>
-  <si>
-    <t>35.83116</t>
-  </si>
-  <si>
-    <t>127.11505</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>효자도서관</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 우전로 181, 효자도서관 (효자동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동2가 1314-9 효자도서관</t>
-  </si>
-  <si>
-    <t>38.81112</t>
-  </si>
-  <si>
-    <t>127.10075</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>전주시립도서관 꽃심</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 백제대로 306(중화산동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 중화산동2가 산 66</t>
-  </si>
-  <si>
-    <t>35.82048</t>
-  </si>
-  <si>
-    <t>127.12359</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>완산구청 3층 정보화교육장</t>
-  </si>
-  <si>
-    <t>edu</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서원로 232, 완산구청 (효자동1가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동1가 595 완산구청</t>
-  </si>
-  <si>
-    <t>063-220-5300</t>
-  </si>
-  <si>
-    <t>35.81239</t>
-  </si>
-  <si>
-    <t>127.11982</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>효자5동주민센터</t>
-  </si>
-  <si>
-    <t>hyoja5</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 우전로 259, 효자5동주민센터 (효자동2가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 효자동2가 1233-1 효자5동주민센터</t>
-  </si>
-  <si>
-    <t>35.81784</t>
-  </si>
-  <si>
-    <t>127.10152</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>서학동예술마을</t>
-  </si>
-  <si>
-    <t>동서학동주민센터 옥상 외 3개소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서학3길 45, 일원 (서서학동)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 서서학동 3-6 서서학파출소</t>
-  </si>
-  <si>
-    <t>35.80884</t>
-  </si>
-  <si>
-    <t>127.15190</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>객리단길</t>
-  </si>
-  <si>
-    <t>어부바식당앞 외 3개소</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전주객사1길 12-7, 일원 (다가동3가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 다가동3가 24-1</t>
-  </si>
-  <si>
-    <t>35.81715</t>
-  </si>
-  <si>
-    <t>127.14027</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>아동청소년센터(야호학교)</t>
-  </si>
-  <si>
-    <t>교육시설</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 진버들5길 15-1(인후동1가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 덕진구 인후동1가 807-4</t>
-  </si>
-  <si>
-    <t>35.83649</t>
-  </si>
-  <si>
-    <t>127.16437</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>풍남문광장</t>
-  </si>
-  <si>
-    <t>광장</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 풍남문2길 105-6(전동3가)</t>
-  </si>
-  <si>
-    <t>전북특별자치도 전주시 완산구 전동3가 77</t>
-  </si>
-  <si>
-    <t>35.81401</t>
-  </si>
-  <si>
-    <t>127.14809</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2153,6 +2107,7 @@
   <dimension ref="A1:N86"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
@@ -2231,33 +2186,33 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>553</v>
       </c>
       <c r="I2" t="s">
+        <v>555</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
+      <c r="M2">
+        <v>35.80883</v>
+      </c>
+      <c r="N2">
+        <v>127.14798999999999</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -2275,36 +2230,36 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>553</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>556</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
         <v>24</v>
       </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" t="s">
-        <v>33</v>
+      <c r="M3">
+        <v>35.791449999999998</v>
+      </c>
+      <c r="N3">
+        <v>127.13488</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -2313,42 +2268,42 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>38</v>
+        <v>554</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>557</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" t="s">
-        <v>44</v>
+        <v>34</v>
+      </c>
+      <c r="M4">
+        <v>35.817671799999999</v>
+      </c>
+      <c r="N4">
+        <v>127.1015345</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -2357,42 +2312,42 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
         <v>41</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
@@ -2401,42 +2356,42 @@
         <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" t="s">
-        <v>58</v>
+        <v>34</v>
+      </c>
+      <c r="M6">
+        <v>35.806837799999997</v>
+      </c>
+      <c r="N6">
+        <v>127.1195137</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
@@ -2445,42 +2400,42 @@
         <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="N7" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
@@ -2489,42 +2444,42 @@
         <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="J8" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" t="s">
-        <v>71</v>
-      </c>
-      <c r="N8" t="s">
-        <v>72</v>
+        <v>34</v>
+      </c>
+      <c r="M8">
+        <v>35.796862599999997</v>
+      </c>
+      <c r="N8">
+        <v>127.1143079</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
@@ -2533,42 +2488,42 @@
         <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -2577,42 +2532,42 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="N10" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -2621,42 +2576,42 @@
         <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="N11" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -2665,42 +2620,42 @@
         <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
         <v>20</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="K12" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -2709,42 +2664,42 @@
         <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>42</v>
-      </c>
-      <c r="M13" t="s">
-        <v>106</v>
-      </c>
-      <c r="N13" t="s">
-        <v>107</v>
+        <v>34</v>
+      </c>
+      <c r="M13">
+        <v>35.798066200000001</v>
+      </c>
+      <c r="N13">
+        <v>127.14032109999999</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -2753,42 +2708,42 @@
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="N14" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -2797,42 +2752,42 @@
         <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I15" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="J15" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M15" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N15" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -2841,42 +2796,42 @@
         <v>18</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I16" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="N16" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B17" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -2885,42 +2840,42 @@
         <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="I17" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="J17" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="K17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M17" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="N17" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -2929,42 +2884,42 @@
         <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G18" t="s">
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I18" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="J18" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="K18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M18" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="N18" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -2973,42 +2928,42 @@
         <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G19" t="s">
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="J19" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="N19" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -3017,42 +2972,42 @@
         <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
         <v>20</v>
       </c>
       <c r="H20" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="I20" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="J20" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="K20" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="N20" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -3061,42 +3016,42 @@
         <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
         <v>20</v>
       </c>
       <c r="H21" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="I21" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="J21" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="K21" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -3105,42 +3060,42 @@
         <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
         <v>20</v>
       </c>
       <c r="H22" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="J22" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="K22" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>42</v>
-      </c>
-      <c r="M22" t="s">
-        <v>169</v>
-      </c>
-      <c r="N22" t="s">
-        <v>170</v>
+        <v>34</v>
+      </c>
+      <c r="M22">
+        <v>35.812153000000002</v>
+      </c>
+      <c r="N22">
+        <v>127.11980250000001</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -3149,42 +3104,42 @@
         <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H23" t="s">
         <v>21</v>
       </c>
       <c r="I23" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="J23" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K23" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L23" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M23" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="N23" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -3193,42 +3148,42 @@
         <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H24" t="s">
         <v>21</v>
       </c>
       <c r="I24" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="J24" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K24" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L24" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M24" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="N24" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B25" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -3237,42 +3192,42 @@
         <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G25" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H25" t="s">
         <v>21</v>
       </c>
       <c r="I25" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="J25" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K25" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s">
-        <v>177</v>
-      </c>
-      <c r="M25" t="s">
-        <v>178</v>
+        <v>159</v>
+      </c>
+      <c r="M25">
+        <v>35.829450999999999</v>
       </c>
       <c r="N25" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -3281,42 +3236,42 @@
         <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H26" t="s">
         <v>21</v>
       </c>
       <c r="I26" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="J26" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K26" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L26" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M26" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="N26" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C27" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -3325,7 +3280,7 @@
         <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G27" t="s">
         <v>20</v>
@@ -3334,33 +3289,33 @@
         <v>21</v>
       </c>
       <c r="I27" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="J27" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="K27" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M27" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="N27" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -3369,7 +3324,7 @@
         <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G28" t="s">
         <v>20</v>
@@ -3378,33 +3333,33 @@
         <v>21</v>
       </c>
       <c r="I28" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="J28" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="K28" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L28" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M28" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="N28" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -3413,42 +3368,42 @@
         <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
         <v>20</v>
       </c>
       <c r="H29" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="I29" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="J29" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="K29" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L29" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M29" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="N29" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -3457,42 +3412,42 @@
         <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G30" t="s">
         <v>20</v>
       </c>
       <c r="H30" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="I30" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="J30" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="K30" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L30" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M30" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
       <c r="N30" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -3501,42 +3456,42 @@
         <v>18</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G31" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H31" t="s">
         <v>21</v>
       </c>
       <c r="I31" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="J31" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="K31" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L31" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M31" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="N31" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="B32" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -3545,42 +3500,42 @@
         <v>18</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H32" t="s">
         <v>21</v>
       </c>
       <c r="I32" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="J32" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="K32" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L32" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M32" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="N32" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -3589,42 +3544,42 @@
         <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
         <v>20</v>
       </c>
       <c r="H33" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="I33" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="K33" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L33" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M33" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -3633,42 +3588,42 @@
         <v>18</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I34" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="J34" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="K34" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L34" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M34" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="N34" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -3677,42 +3632,42 @@
         <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
         <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I35" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="J35" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="K35" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M35" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="N35" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -3721,7 +3676,7 @@
         <v>18</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G36" t="s">
         <v>20</v>
@@ -3730,33 +3685,33 @@
         <v>21</v>
       </c>
       <c r="I36" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="J36" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="K36" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L36" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M36" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="N36" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -3765,42 +3720,42 @@
         <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G37" t="s">
         <v>20</v>
       </c>
       <c r="H37" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I37" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="J37" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="K37" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L37" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M37" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="N37" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -3809,42 +3764,42 @@
         <v>18</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H38" t="s">
         <v>21</v>
       </c>
       <c r="I38" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="J38" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="K38" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L38" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M38" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="N38" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B39" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -3853,42 +3808,42 @@
         <v>18</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G39" t="s">
         <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I39" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="J39" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="K39" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L39" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M39" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="N39" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B40" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="C40" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -3897,42 +3852,42 @@
         <v>18</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G40" t="s">
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I40" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="J40" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="K40" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L40" t="s">
-        <v>177</v>
-      </c>
-      <c r="M40" t="s">
-        <v>273</v>
-      </c>
-      <c r="N40" t="s">
-        <v>274</v>
+        <v>159</v>
+      </c>
+      <c r="M40">
+        <v>35.857094699999998</v>
+      </c>
+      <c r="N40">
+        <v>127.1210231</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="B41" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C41" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -3941,42 +3896,42 @@
         <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G41" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H41" t="s">
         <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="J41" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="K41" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L41" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M41" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="N41" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="B42" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="C42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -3985,42 +3940,42 @@
         <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G42" t="s">
         <v>20</v>
       </c>
       <c r="H42" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="I42" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="J42" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="K42" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L42" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M42" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="N42" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="B43" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -4029,42 +3984,42 @@
         <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G43" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H43" t="s">
         <v>21</v>
       </c>
       <c r="I43" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="J43" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="K43" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L43" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M43" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="N43" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="B44" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -4073,42 +4028,42 @@
         <v>18</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="H44" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="I44" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="J44" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="K44" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="M44" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="N44" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C45" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -4126,33 +4081,33 @@
         <v>21</v>
       </c>
       <c r="I45" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="J45" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="K45" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" t="s">
-        <v>306</v>
-      </c>
-      <c r="N45" t="s">
-        <v>307</v>
+        <v>24</v>
+      </c>
+      <c r="M45">
+        <v>35.812829800000003</v>
+      </c>
+      <c r="N45">
+        <v>127.1571308</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="C46" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -4161,7 +4116,7 @@
         <v>18</v>
       </c>
       <c r="F46" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G46" t="s">
         <v>20</v>
@@ -4170,33 +4125,33 @@
         <v>21</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="J46" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="K46" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M46" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="B47" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="C47" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -4214,33 +4169,33 @@
         <v>21</v>
       </c>
       <c r="I47" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="J47" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="K47" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="N47" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="B48" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="C48" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -4249,42 +4204,42 @@
         <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G48" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H48" t="s">
         <v>21</v>
       </c>
       <c r="I48" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
       <c r="J48" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="K48" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M48" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="N48" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="B49" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="C49" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -4293,39 +4248,39 @@
         <v>18</v>
       </c>
       <c r="F49" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G49" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H49" t="s">
         <v>21</v>
       </c>
       <c r="I49" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
       <c r="J49" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="K49" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M49" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="N49" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="B50" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="C50" t="s">
         <v>16</v>
@@ -4337,42 +4292,42 @@
         <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G50" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H50" t="s">
         <v>21</v>
       </c>
       <c r="I50" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="J50" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="K50" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M50" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
       <c r="N50" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B51" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="C51" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -4381,7 +4336,7 @@
         <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G51" t="s">
         <v>20</v>
@@ -4390,30 +4345,30 @@
         <v>21</v>
       </c>
       <c r="I51" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
       <c r="J51" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="K51" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M51" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="N51" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -4425,39 +4380,39 @@
         <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G52" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H52" t="s">
         <v>21</v>
       </c>
       <c r="I52" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="J52" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="K52" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M52" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="N52" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="B53" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
@@ -4472,39 +4427,39 @@
         <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H53" t="s">
         <v>21</v>
       </c>
       <c r="I53" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="J53" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
       <c r="K53" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="N53" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="B54" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="C54" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
@@ -4513,39 +4468,39 @@
         <v>18</v>
       </c>
       <c r="F54" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
       <c r="G54" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H54" t="s">
         <v>21</v>
       </c>
       <c r="I54" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="J54" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
       <c r="K54" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M54" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="N54" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="B55" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="C55" t="s">
         <v>16</v>
@@ -4560,36 +4515,36 @@
         <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H55" t="s">
         <v>21</v>
       </c>
       <c r="I55" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="J55" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="K55" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M55" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="N55" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
@@ -4604,36 +4559,36 @@
         <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H56" t="s">
         <v>21</v>
       </c>
       <c r="I56" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="J56" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="K56" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M56" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="N56" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -4648,36 +4603,36 @@
         <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H57" t="s">
         <v>21</v>
       </c>
       <c r="I57" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="J57" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="K57" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M57" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="N57" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="B58" t="s">
-        <v>387</v>
+        <v>365</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
@@ -4692,39 +4647,39 @@
         <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H58" t="s">
         <v>21</v>
       </c>
       <c r="I58" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="J58" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="K58" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M58" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="N58" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="C59" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -4733,7 +4688,7 @@
         <v>18</v>
       </c>
       <c r="F59" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G59" t="s">
         <v>20</v>
@@ -4742,33 +4697,33 @@
         <v>21</v>
       </c>
       <c r="I59" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="J59" t="s">
-        <v>396</v>
+        <v>374</v>
       </c>
       <c r="K59" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M59" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="N59" t="s">
-        <v>398</v>
+        <v>376</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B60" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="C60" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="D60" t="s">
         <v>17</v>
@@ -4777,7 +4732,7 @@
         <v>18</v>
       </c>
       <c r="F60" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="G60" t="s">
         <v>20</v>
@@ -4786,33 +4741,33 @@
         <v>21</v>
       </c>
       <c r="I60" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="J60" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="K60" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M60" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="N60" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>408</v>
+        <v>386</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -4821,7 +4776,7 @@
         <v>18</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G61" t="s">
         <v>20</v>
@@ -4830,33 +4785,33 @@
         <v>21</v>
       </c>
       <c r="I61" t="s">
-        <v>409</v>
+        <v>387</v>
       </c>
       <c r="J61" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="K61" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M61" t="s">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="N61" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="B62" t="s">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="C62" t="s">
-        <v>415</v>
+        <v>393</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -4868,36 +4823,36 @@
         <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H62" t="s">
         <v>21</v>
       </c>
       <c r="I62" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="J62" t="s">
-        <v>417</v>
+        <v>395</v>
       </c>
       <c r="K62" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M62" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="N62" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="B63" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
       <c r="C63" t="s">
         <v>16</v>
@@ -4909,39 +4864,39 @@
         <v>18</v>
       </c>
       <c r="F63" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G63" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H63" t="s">
         <v>21</v>
       </c>
       <c r="I63" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="J63" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="K63" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M63" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="N63" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="B64" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="C64" t="s">
         <v>16</v>
@@ -4953,39 +4908,39 @@
         <v>18</v>
       </c>
       <c r="F64" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G64" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H64" t="s">
         <v>21</v>
       </c>
       <c r="I64" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="J64" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="K64" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M64" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="N64" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="C65" t="s">
         <v>16</v>
@@ -4997,42 +4952,42 @@
         <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G65" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H65" t="s">
         <v>21</v>
       </c>
       <c r="I65" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="J65" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="K65" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M65" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="N65" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="C66" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="D66" t="s">
         <v>17</v>
@@ -5041,42 +4996,42 @@
         <v>18</v>
       </c>
       <c r="F66" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G66" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H66" t="s">
         <v>21</v>
       </c>
       <c r="I66" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="J66" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="K66" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M66" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="N66" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="B67" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="C67" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D67" t="s">
         <v>17</v>
@@ -5085,42 +5040,42 @@
         <v>18</v>
       </c>
       <c r="F67" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G67" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H67" t="s">
         <v>21</v>
       </c>
       <c r="I67" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="J67" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="K67" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M67" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="N67" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B68" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="C68" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="D68" t="s">
         <v>17</v>
@@ -5129,42 +5084,42 @@
         <v>18</v>
       </c>
       <c r="F68" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G68" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H68" t="s">
         <v>21</v>
       </c>
       <c r="I68" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="J68" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="K68" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M68" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="N68" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="C69" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="D69" t="s">
         <v>17</v>
@@ -5173,7 +5128,7 @@
         <v>18</v>
       </c>
       <c r="F69" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="G69" t="s">
         <v>20</v>
@@ -5182,33 +5137,33 @@
         <v>21</v>
       </c>
       <c r="I69" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="J69" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="K69" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M69" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="N69" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="C70" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="D70" t="s">
         <v>17</v>
@@ -5217,7 +5172,7 @@
         <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="G70" t="s">
         <v>20</v>
@@ -5226,30 +5181,30 @@
         <v>21</v>
       </c>
       <c r="I70" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="J70" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="K70" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L70" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M70" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="N70" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="C71" t="s">
         <v>16</v>
@@ -5270,33 +5225,33 @@
         <v>21</v>
       </c>
       <c r="I71" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="J71" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="K71" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M71" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="N71" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="B72" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="C72" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="D72" t="s">
         <v>17</v>
@@ -5314,33 +5269,33 @@
         <v>21</v>
       </c>
       <c r="I72" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="J72" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="K72" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M72" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
       <c r="B73" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="C73" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="D73" t="s">
         <v>17</v>
@@ -5358,30 +5313,30 @@
         <v>21</v>
       </c>
       <c r="I73" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="J73" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="K73" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M73" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="N73" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="C74" t="s">
         <v>16</v>
@@ -5402,30 +5357,30 @@
         <v>21</v>
       </c>
       <c r="I74" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="J74" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="K74" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="L74" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M74" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="N74" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C75" t="s">
         <v>16</v>
@@ -5446,30 +5401,30 @@
         <v>21</v>
       </c>
       <c r="I75" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="J75" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
         <v>24</v>
       </c>
-      <c r="L75" t="s">
-        <v>25</v>
-      </c>
       <c r="M75" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="N75" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="C76" t="s">
         <v>16</v>
@@ -5490,30 +5445,30 @@
         <v>21</v>
       </c>
       <c r="I76" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="J76" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
         <v>24</v>
       </c>
-      <c r="L76" t="s">
-        <v>25</v>
-      </c>
       <c r="M76" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="N76" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="B77" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="C77" t="s">
         <v>16</v>
@@ -5534,30 +5489,30 @@
         <v>21</v>
       </c>
       <c r="I77" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="J77" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
         <v>24</v>
       </c>
-      <c r="L77" t="s">
-        <v>25</v>
-      </c>
       <c r="M77" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="N77" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="C78" t="s">
         <v>16</v>
@@ -5578,30 +5533,30 @@
         <v>21</v>
       </c>
       <c r="I78" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="J78" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
         <v>24</v>
       </c>
-      <c r="L78" t="s">
-        <v>25</v>
-      </c>
       <c r="M78" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="N78" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="B79" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="C79" t="s">
         <v>16</v>
@@ -5622,30 +5577,30 @@
         <v>21</v>
       </c>
       <c r="I79" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="J79" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
         <v>24</v>
       </c>
-      <c r="L79" t="s">
-        <v>25</v>
-      </c>
       <c r="M79" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="C80" t="s">
         <v>16</v>
@@ -5666,30 +5621,30 @@
         <v>21</v>
       </c>
       <c r="I80" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="J80" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
         <v>24</v>
       </c>
-      <c r="L80" t="s">
-        <v>25</v>
-      </c>
       <c r="M80" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="N80" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="B81" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="C81" t="s">
         <v>16</v>
@@ -5701,42 +5656,42 @@
         <v>18</v>
       </c>
       <c r="F81" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G81" t="s">
         <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="I81" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="J81" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="K81" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="L81" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="M81" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="N81" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="B82" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
         <v>17</v>
@@ -5745,42 +5700,42 @@
         <v>18</v>
       </c>
       <c r="F82" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G82" t="s">
         <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="I82" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="J82" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="K82" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="L82" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="M82" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="N82" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="B83" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="C83" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="D83" t="s">
         <v>17</v>
@@ -5792,39 +5747,39 @@
         <v>19</v>
       </c>
       <c r="G83" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="H83" t="s">
         <v>21</v>
       </c>
       <c r="I83" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="J83" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
         <v>24</v>
       </c>
-      <c r="L83" t="s">
-        <v>25</v>
-      </c>
       <c r="M83" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="N83" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="C84" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
@@ -5833,7 +5788,7 @@
         <v>18</v>
       </c>
       <c r="F84" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="G84" t="s">
         <v>20</v>
@@ -5842,30 +5797,30 @@
         <v>21</v>
       </c>
       <c r="I84" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="J84" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
         <v>24</v>
       </c>
-      <c r="L84" t="s">
-        <v>25</v>
-      </c>
       <c r="M84" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="N84" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="B85" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="C85" t="s">
         <v>16</v>
@@ -5877,7 +5832,7 @@
         <v>18</v>
       </c>
       <c r="F85" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="G85" t="s">
         <v>20</v>
@@ -5886,33 +5841,33 @@
         <v>21</v>
       </c>
       <c r="I85" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="J85" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
         <v>24</v>
       </c>
-      <c r="L85" t="s">
-        <v>25</v>
-      </c>
       <c r="M85" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="N85" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="B86" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="C86" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="D86" t="s">
         <v>17</v>
@@ -5930,22 +5885,22 @@
         <v>21</v>
       </c>
       <c r="I86" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="J86" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
         <v>24</v>
       </c>
-      <c r="L86" t="s">
-        <v>25</v>
-      </c>
       <c r="M86" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="N86" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
